--- a/data/trans_orig/IMC_inf_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>23793</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37387</t>
+          <t>37480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10954</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20608</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>35977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,47 +1430,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>15,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>44357</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>35519</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>54124</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>15,5%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>44357</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>35767</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>55885</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60136</t>
+          <t>59261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84233</t>
+          <t>84547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>39377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>24722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>39159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>59801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53811</t>
+          <t>53580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50547</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>73271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98510</t>
+          <t>98597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104939</t>
+          <t>104796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128968</t>
+          <t>129532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101217</t>
+          <t>100759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124922</t>
+          <t>125019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213128</t>
+          <t>214577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>245744</t>
+          <t>246970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18042</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>33266</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27653</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28588</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47307</t>
+          <t>46446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26845</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>42914</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34558</t>
+          <t>34544</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50681</t>
+          <t>52327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65415</t>
+          <t>64105</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88287</t>
+          <t>88127</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60104</t>
+          <t>60607</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77984</t>
+          <t>78913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50772</t>
+          <t>50469</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68822</t>
+          <t>69006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117061</t>
+          <t>117378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142072</t>
+          <t>142901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,82 +2907,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>8499</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>14142</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>13565</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>8837</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>20117</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>8499</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>4565</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>14974</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>13565</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>8932</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>20744</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36641</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64953</t>
+          <t>65056</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86482</t>
+          <t>86939</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>89424</t>
+          <t>91149</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>118175</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146038</t>
+          <t>146640</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>163991</t>
+          <t>165034</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103254</t>
+          <t>103025</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126020</t>
+          <t>124941</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>254957</t>
+          <t>253792</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283178</t>
+          <t>283226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>28989</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47581</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>71906</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82773</t>
+          <t>81982</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114281</t>
+          <t>111985</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>45556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70187</t>
+          <t>68816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63978</t>
+          <t>63107</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>95471</t>
+          <t>93858</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129163</t>
+          <t>126870</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96390</t>
+          <t>95845</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>125929</t>
+          <t>126992</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>145018</t>
+          <t>145617</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>181033</t>
+          <t>179194</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>248952</t>
+          <t>249523</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>293530</t>
+          <t>296990</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>336336</t>
+          <t>337753</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>373170</t>
+          <t>374853</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>284688</t>
+          <t>286140</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>323452</t>
+          <t>326805</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>630973</t>
+          <t>631960</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>686263</t>
+          <t>689398</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35497</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>57309</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>17463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>19758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32545</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34371</t>
+          <t>35093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>40885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61590</t>
+          <t>62045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63863</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91179</t>
+          <t>91190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23107</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>29581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50108</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59150</t>
+          <t>58391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84067</t>
+          <t>84300</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26920</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44403</t>
+          <t>46677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39230</t>
+          <t>38478</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60477</t>
+          <t>59297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72039</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96839</t>
+          <t>97191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85378</t>
+          <t>83134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108397</t>
+          <t>107522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68311</t>
+          <t>67976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92408</t>
+          <t>93103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159377</t>
+          <t>157861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195436</t>
+          <t>192401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>28864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20096</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>25573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>30773</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28614</t>
+          <t>28780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>34026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54274</t>
+          <t>54350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35494</t>
+          <t>35867</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53773</t>
+          <t>55769</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26597</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44871</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68328</t>
+          <t>66923</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92761</t>
+          <t>92653</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52896</t>
+          <t>52818</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71897</t>
+          <t>72411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56488</t>
+          <t>56918</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76621</t>
+          <t>75566</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117038</t>
+          <t>116415</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144392</t>
+          <t>144242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>560</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14308</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25293</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24290</t>
+          <t>23988</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40668</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>41706</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61427</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>70868</t>
+          <t>70672</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>96602</t>
+          <t>96472</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100106</t>
+          <t>100396</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118972</t>
+          <t>119668</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87382</t>
+          <t>87598</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107321</t>
+          <t>107952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>194817</t>
+          <t>192918</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222983</t>
+          <t>221640</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48738</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58626</t>
+          <t>57600</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83530</t>
+          <t>84310</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>92761</t>
+          <t>92273</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>126248</t>
+          <t>125713</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>53881</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>78965</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,49 +7231,49 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>70773</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>58276</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>82640</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>14,85%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>70773</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>58143</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>83679</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>195</t>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>118671</t>
+          <t>118866</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>156882</t>
+          <t>155085</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103521</t>
+          <t>105510</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134384</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>123523</t>
+          <t>123483</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>157252</t>
+          <t>157718</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>235970</t>
+          <t>235056</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>281146</t>
+          <t>278992</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>266822</t>
+          <t>264766</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>237934</t>
+          <t>236549</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>275770</t>
+          <t>275456</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>514826</t>
+          <t>514186</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>568757</t>
+          <t>567982</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>27464</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51319</t>
+          <t>52320</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>33546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>25049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>26857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>45044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65958</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35810</t>
+          <t>35121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>37546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43464</t>
+          <t>43673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65330</t>
+          <t>65634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>22786</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39095</t>
+          <t>39786</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37837</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>56895</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89237</t>
+          <t>90748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89353</t>
+          <t>89698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111135</t>
+          <t>111866</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88661</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112797</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182692</t>
+          <t>183906</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216041</t>
+          <t>216496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35004</t>
+          <t>34050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21684</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9889</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>23729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39727</t>
+          <t>41394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35948</t>
+          <t>35912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57731</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>37127</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56525</t>
+          <t>57079</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35908</t>
+          <t>36553</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55640</t>
+          <t>55242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>79241</t>
+          <t>78876</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>107257</t>
+          <t>106413</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89028</t>
+          <t>88642</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110472</t>
+          <t>110736</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68580</t>
+          <t>68768</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90302</t>
+          <t>90649</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165109</t>
+          <t>164870</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>194486</t>
+          <t>194584</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15327</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,82 +10191,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>7209</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3640</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>12462</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>16691</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>10965</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>24846</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>3,55%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>7209</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3566</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>14081</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>16691</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>11003</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>24909</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>16827</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>32381</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50921</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53258</t>
+          <t>52743</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76095</t>
+          <t>75524</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106345</t>
+          <t>105143</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123649</t>
+          <t>124107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84551</t>
+          <t>84324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>104611</t>
+          <t>104438</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196444</t>
+          <t>198209</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>224045</t>
+          <t>225838</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>73,02%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>23865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>37075</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40515</t>
+          <t>40101</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>63514</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67191</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94749</t>
+          <t>95879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68207</t>
+          <t>67678</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57885</t>
+          <t>57545</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83760</t>
+          <t>83776</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>107131</t>
+          <t>106281</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>142754</t>
+          <t>141009</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92716</t>
+          <t>91196</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121706</t>
+          <t>122103</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>121423</t>
+          <t>124718</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>157620</t>
+          <t>159599</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>225360</t>
+          <t>223298</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>271412</t>
+          <t>269011</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>310857</t>
+          <t>311662</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>347698</t>
+          <t>349488</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>269854</t>
+          <t>270464</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>309996</t>
+          <t>308918</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>590482</t>
+          <t>592724</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>645371</t>
+          <t>646396</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>45229</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>47083</t>
+          <t>47705</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>71861</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>340</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17251</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>29172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>31112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50390</t>
+          <t>48380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33777</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33623</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>52717</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>29558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40427</t>
+          <t>41768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42713</t>
+          <t>43124</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65498</t>
+          <t>65408</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66169</t>
+          <t>65479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86114</t>
+          <t>84333</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>68313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90976</t>
+          <t>90387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>140479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170018</t>
+          <t>168916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,77%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>40620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57818</t>
+          <t>56513</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29935</t>
+          <t>30622</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51372</t>
+          <t>52546</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28880</t>
+          <t>28627</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48282</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64412</t>
+          <t>63766</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94404</t>
+          <t>93475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86840</t>
+          <t>85659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109460</t>
+          <t>109101</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90120</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>115183</t>
+          <t>115913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184768</t>
+          <t>184152</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>219019</t>
+          <t>216663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>18083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9851</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>544</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40695</t>
+          <t>40149</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45082</t>
+          <t>44595</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88757</t>
+          <t>87293</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80586</t>
+          <t>79543</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>124959</t>
+          <t>123265</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>158197</t>
+          <t>159198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198888</t>
+          <t>200264</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>144575</t>
+          <t>146217</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183559</t>
+          <t>183716</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>316137</t>
+          <t>316358</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>375442</t>
+          <t>375815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47500</t>
+          <t>47133</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73308</t>
+          <t>72747</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47787</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49063</t>
+          <t>49780</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75861</t>
+          <t>75452</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>92485</t>
+          <t>93889</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>95399</t>
+          <t>94933</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>136608</t>
+          <t>135024</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>80967</t>
+          <t>81174</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>119258</t>
+          <t>117613</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>122706</t>
+          <t>122122</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>166564</t>
+          <t>167659</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>213713</t>
+          <t>215339</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>272799</t>
+          <t>272458</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>341443</t>
+          <t>343494</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>397804</t>
+          <t>399413</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>329371</t>
+          <t>330449</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>384852</t>
+          <t>384480</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,47 +14776,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>723984</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>689942</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>768008</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>58,95%</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>723984</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>688594</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>763954</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>58,95%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64588</t>
+          <t>65499</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52633</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70638</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>109548</t>
+          <t>107981</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_inf_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Edad-trans_orig.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>113349</v>
+        <v>113999</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>101274</v>
+        <v>102004</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>125620</v>
+        <v>125959</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4946098549306214</v>
+        <v>0.4974465480143367</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4419169940625054</v>
+        <v>0.4451031065679448</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5481544851815371</v>
+        <v>0.5496322909642173</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>174</v>
@@ -1415,25 +1415,25 @@
         <v>0.5558711752162511</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>229907</v>
+        <v>230557</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>213511</v>
+        <v>214186</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>248712</v>
+        <v>249707</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4991786211627334</v>
+        <v>0.5005900893339148</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.4635799722133332</v>
+        <v>0.465044771783221</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5400079174150743</v>
+        <v>0.5421676520492191</v>
       </c>
     </row>
     <row r="14">
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>12550</v>
+        <v>11900</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>7768</v>
+        <v>7314</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>18665</v>
+        <v>18018</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.05476463566009682</v>
+        <v>0.05192794257638147</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.03389483224602147</v>
+        <v>0.03191569717940371</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.08144738387640692</v>
+        <v>0.07862466336429495</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>19</v>
@@ -1486,25 +1486,25 @@
         <v>0.07917421922748379</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>24762</v>
+        <v>24112</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>17794</v>
+        <v>17551</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>33364</v>
+        <v>33024</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.05376439783877166</v>
+        <v>0.05235292966759021</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.0386336056873656</v>
+        <v>0.0381071723977201</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.07244058808170654</v>
+        <v>0.07170138800694123</v>
       </c>
     </row>
     <row r="15">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2639,25 +2639,25 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>304213</v>
+        <v>304863</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>285570</v>
+        <v>286131</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>324293</v>
+        <v>324710</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.5024551392778183</v>
+        <v>0.5035288487457855</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.4716626792796453</v>
+        <v>0.4725897824735413</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5356197657406884</v>
+        <v>0.5363088091232465</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>525</v>
@@ -2681,25 +2681,25 @@
         <v>0.6454744660949693</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>659528</v>
+        <v>660178</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>633140</v>
+        <v>633820</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>687943</v>
+        <v>688456</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.5572576635126306</v>
+        <v>0.5578069385938749</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.5349609214065915</v>
+        <v>0.5355359463257564</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.5812662489721956</v>
+        <v>0.5816993726167565</v>
       </c>
     </row>
     <row r="32">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>26250</v>
+        <v>25599</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>19267</v>
+        <v>18573</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>34699</v>
+        <v>34180</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.04335525635786645</v>
+        <v>0.04228154688989916</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.03182265127449958</v>
+        <v>0.03067645825931641</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.05731068622694988</v>
+        <v>0.0564528716715501</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>29</v>
@@ -2752,25 +2752,25 @@
         <v>0.0458607535520415</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R32" s="5" t="n">
-        <v>45282</v>
+        <v>44632</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>36104</v>
+        <v>35378</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>57176</v>
+        <v>56272</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.03826000231423884</v>
+        <v>0.03771072723299453</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.03050524197936881</v>
+        <v>0.02989174778838683</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.04830994509272634</v>
+        <v>0.04754635947722598</v>
       </c>
     </row>
     <row r="33">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
